--- a/Album_CopaMundo2026_Completo.xlsx
+++ b/Album_CopaMundo2026_Completo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julian.bello\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elcondor-my.sharepoint.com/personal/julian_bello_elcondor_com/Documents/Documentos/fifa2026album/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C7637F-F8E3-4ED6-89F2-A5C6BFFEA884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{53C7637F-F8E3-4ED6-89F2-A5C6BFFEA884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E97D97-4E38-432E-8C91-38F48A13ACA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="73">
   <si>
     <t>Laminas</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>Pagina</t>
+  </si>
+  <si>
+    <t>Estadio</t>
   </si>
 </sst>
 </file>
@@ -673,10 +676,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
@@ -689,11 +692,11 @@
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>5</v>
@@ -707,10 +710,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>5</v>
@@ -723,11 +726,11 @@
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>5</v>
@@ -741,10 +744,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>5</v>
@@ -757,11 +760,11 @@
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>5</v>
@@ -775,10 +778,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>5</v>
@@ -791,11 +794,11 @@
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>5</v>
@@ -809,10 +812,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>5</v>
@@ -825,11 +828,11 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>5</v>
@@ -843,10 +846,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>5</v>
@@ -859,11 +862,11 @@
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>5</v>
@@ -877,10 +880,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
@@ -893,11 +896,11 @@
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>5</v>
@@ -911,10 +914,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>5</v>
@@ -2231,13 +2234,13 @@
       <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B92" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E92" s="4">
@@ -2249,13 +2252,13 @@
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" s="5" t="s">
+      <c r="B93" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E93" s="4">
@@ -2267,13 +2270,13 @@
       <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="B94" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E94" s="4">
@@ -2285,13 +2288,13 @@
       <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C95" s="5" t="s">
+      <c r="B95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E95" s="4">
@@ -2303,13 +2306,13 @@
       <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="B96" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="4">
@@ -2321,13 +2324,13 @@
       <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C97" s="5" t="s">
+      <c r="B97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="4">
@@ -2339,13 +2342,13 @@
       <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B98" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="4">
@@ -2357,13 +2360,13 @@
       <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C99" s="5" t="s">
+      <c r="B99" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E99" s="4">
@@ -2375,13 +2378,13 @@
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="B100" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E100" s="4">
@@ -2393,13 +2396,13 @@
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C101" s="5" t="s">
+      <c r="B101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="4">
@@ -2411,13 +2414,13 @@
       <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="B102" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E102" s="4">
@@ -2429,13 +2432,13 @@
       <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C103" s="5" t="s">
+      <c r="B103" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E103" s="4">
@@ -2447,13 +2450,13 @@
       <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="B104" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E104" s="4">
@@ -2465,13 +2468,13 @@
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C105" s="5" t="s">
+      <c r="B105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E105" s="4">
@@ -2483,13 +2486,13 @@
       <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="B106" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="4">
@@ -2501,13 +2504,13 @@
       <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C107" s="5" t="s">
+      <c r="B107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="4">
@@ -2519,13 +2522,13 @@
       <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C108" s="2" t="s">
+      <c r="B108" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="4">
@@ -2537,13 +2540,13 @@
       <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C109" s="5" t="s">
+      <c r="B109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E109" s="4">
@@ -2555,13 +2558,13 @@
       <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="B110" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E110" s="4">
@@ -2573,13 +2576,13 @@
       <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111" s="5" t="s">
+      <c r="B111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E111" s="4">
@@ -2591,13 +2594,13 @@
       <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="B112" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E112" s="4">
@@ -2609,13 +2612,13 @@
       <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C113" s="5" t="s">
+      <c r="B113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E113" s="4">
@@ -2627,13 +2630,13 @@
       <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C114" s="2" t="s">
+      <c r="B114" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="4">
@@ -2645,13 +2648,13 @@
       <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C115" s="5" t="s">
+      <c r="B115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="4">
@@ -2663,13 +2666,13 @@
       <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C116" s="2" t="s">
+      <c r="B116" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="4">
@@ -2681,13 +2684,13 @@
       <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="B117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E117" s="4">
@@ -2699,13 +2702,13 @@
       <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="B118" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E118" s="4">
@@ -2717,13 +2720,13 @@
       <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C119" s="5" t="s">
+      <c r="B119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="4">
@@ -2735,13 +2738,13 @@
       <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="B120" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="4">
@@ -2753,13 +2756,13 @@
       <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C121" s="5" t="s">
+      <c r="B121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="4">
@@ -2772,7 +2775,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>17</v>
@@ -2790,7 +2793,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>17</v>
@@ -2808,7 +2811,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>17</v>
@@ -2826,7 +2829,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>17</v>
@@ -2844,7 +2847,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>17</v>
@@ -2862,7 +2865,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>17</v>
@@ -2880,7 +2883,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>17</v>
@@ -2898,7 +2901,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>17</v>
@@ -2916,7 +2919,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>17</v>
@@ -2934,7 +2937,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>17</v>
@@ -2952,7 +2955,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>17</v>
@@ -2970,7 +2973,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>17</v>
@@ -2988,7 +2991,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>17</v>
@@ -3006,7 +3009,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>17</v>
@@ -3024,7 +3027,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>17</v>
@@ -5751,7 +5754,7 @@
         <v>8</v>
       </c>
       <c r="E287" s="4">
-        <f t="shared" ref="E287:E350" si="1">E286+1</f>
+        <f t="shared" ref="E287" si="1">E286+1</f>
         <v>20</v>
       </c>
     </row>
@@ -6821,8 +6824,8 @@
       <c r="A347" s="5">
         <v>346</v>
       </c>
-      <c r="B347" s="6" t="s">
-        <v>39</v>
+      <c r="B347" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C347" s="5" t="s">
         <v>37</v>
@@ -6839,8 +6842,8 @@
       <c r="A348" s="2">
         <v>347</v>
       </c>
-      <c r="B348" s="3" t="s">
-        <v>39</v>
+      <c r="B348" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>37</v>
@@ -6857,8 +6860,8 @@
       <c r="A349" s="5">
         <v>348</v>
       </c>
-      <c r="B349" s="6" t="s">
-        <v>39</v>
+      <c r="B349" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C349" s="5" t="s">
         <v>37</v>
@@ -6875,8 +6878,8 @@
       <c r="A350" s="2">
         <v>349</v>
       </c>
-      <c r="B350" s="3" t="s">
-        <v>39</v>
+      <c r="B350" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>37</v>
@@ -6893,8 +6896,8 @@
       <c r="A351" s="5">
         <v>350</v>
       </c>
-      <c r="B351" s="6" t="s">
-        <v>39</v>
+      <c r="B351" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C351" s="5" t="s">
         <v>37</v>
@@ -6911,8 +6914,8 @@
       <c r="A352" s="2">
         <v>351</v>
       </c>
-      <c r="B352" s="3" t="s">
-        <v>39</v>
+      <c r="B352" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>37</v>
@@ -6929,8 +6932,8 @@
       <c r="A353" s="5">
         <v>352</v>
       </c>
-      <c r="B353" s="6" t="s">
-        <v>39</v>
+      <c r="B353" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C353" s="5" t="s">
         <v>37</v>
@@ -6947,8 +6950,8 @@
       <c r="A354" s="2">
         <v>353</v>
       </c>
-      <c r="B354" s="3" t="s">
-        <v>39</v>
+      <c r="B354" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>37</v>
@@ -6965,8 +6968,8 @@
       <c r="A355" s="5">
         <v>354</v>
       </c>
-      <c r="B355" s="6" t="s">
-        <v>39</v>
+      <c r="B355" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C355" s="5" t="s">
         <v>37</v>
@@ -6983,8 +6986,8 @@
       <c r="A356" s="2">
         <v>355</v>
       </c>
-      <c r="B356" s="3" t="s">
-        <v>39</v>
+      <c r="B356" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>37</v>
@@ -7001,8 +7004,8 @@
       <c r="A357" s="5">
         <v>356</v>
       </c>
-      <c r="B357" s="6" t="s">
-        <v>39</v>
+      <c r="B357" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C357" s="5" t="s">
         <v>37</v>
@@ -7019,8 +7022,8 @@
       <c r="A358" s="2">
         <v>357</v>
       </c>
-      <c r="B358" s="3" t="s">
-        <v>39</v>
+      <c r="B358" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>37</v>
@@ -7037,8 +7040,8 @@
       <c r="A359" s="5">
         <v>358</v>
       </c>
-      <c r="B359" s="6" t="s">
-        <v>39</v>
+      <c r="B359" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C359" s="5" t="s">
         <v>37</v>
@@ -7055,8 +7058,8 @@
       <c r="A360" s="2">
         <v>359</v>
       </c>
-      <c r="B360" s="3" t="s">
-        <v>39</v>
+      <c r="B360" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>37</v>
@@ -7073,8 +7076,8 @@
       <c r="A361" s="5">
         <v>360</v>
       </c>
-      <c r="B361" s="6" t="s">
-        <v>39</v>
+      <c r="B361" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C361" s="5" t="s">
         <v>37</v>
@@ -7091,8 +7094,8 @@
       <c r="A362" s="2">
         <v>361</v>
       </c>
-      <c r="B362" s="3" t="s">
-        <v>40</v>
+      <c r="B362" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>37</v>
@@ -7109,8 +7112,8 @@
       <c r="A363" s="5">
         <v>362</v>
       </c>
-      <c r="B363" s="6" t="s">
-        <v>40</v>
+      <c r="B363" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C363" s="5" t="s">
         <v>37</v>
@@ -7127,8 +7130,8 @@
       <c r="A364" s="2">
         <v>363</v>
       </c>
-      <c r="B364" s="3" t="s">
-        <v>40</v>
+      <c r="B364" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>37</v>
@@ -7145,8 +7148,8 @@
       <c r="A365" s="5">
         <v>364</v>
       </c>
-      <c r="B365" s="6" t="s">
-        <v>40</v>
+      <c r="B365" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C365" s="5" t="s">
         <v>37</v>
@@ -7163,8 +7166,8 @@
       <c r="A366" s="2">
         <v>365</v>
       </c>
-      <c r="B366" s="3" t="s">
-        <v>40</v>
+      <c r="B366" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>37</v>
@@ -7181,8 +7184,8 @@
       <c r="A367" s="5">
         <v>366</v>
       </c>
-      <c r="B367" s="6" t="s">
-        <v>40</v>
+      <c r="B367" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C367" s="5" t="s">
         <v>37</v>
@@ -7199,8 +7202,8 @@
       <c r="A368" s="2">
         <v>367</v>
       </c>
-      <c r="B368" s="3" t="s">
-        <v>40</v>
+      <c r="B368" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>37</v>
@@ -7217,8 +7220,8 @@
       <c r="A369" s="5">
         <v>368</v>
       </c>
-      <c r="B369" s="6" t="s">
-        <v>40</v>
+      <c r="B369" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C369" s="5" t="s">
         <v>37</v>
@@ -7235,8 +7238,8 @@
       <c r="A370" s="2">
         <v>369</v>
       </c>
-      <c r="B370" s="3" t="s">
-        <v>40</v>
+      <c r="B370" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>37</v>
@@ -7253,8 +7256,8 @@
       <c r="A371" s="5">
         <v>370</v>
       </c>
-      <c r="B371" s="6" t="s">
-        <v>40</v>
+      <c r="B371" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C371" s="5" t="s">
         <v>37</v>
@@ -7271,8 +7274,8 @@
       <c r="A372" s="2">
         <v>371</v>
       </c>
-      <c r="B372" s="3" t="s">
-        <v>40</v>
+      <c r="B372" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>37</v>
@@ -7289,8 +7292,8 @@
       <c r="A373" s="5">
         <v>372</v>
       </c>
-      <c r="B373" s="6" t="s">
-        <v>40</v>
+      <c r="B373" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C373" s="5" t="s">
         <v>37</v>
@@ -7307,8 +7310,8 @@
       <c r="A374" s="2">
         <v>373</v>
       </c>
-      <c r="B374" s="3" t="s">
-        <v>40</v>
+      <c r="B374" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>37</v>
@@ -7325,8 +7328,8 @@
       <c r="A375" s="5">
         <v>374</v>
       </c>
-      <c r="B375" s="6" t="s">
-        <v>40</v>
+      <c r="B375" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C375" s="5" t="s">
         <v>37</v>
@@ -7343,8 +7346,8 @@
       <c r="A376" s="2">
         <v>375</v>
       </c>
-      <c r="B376" s="3" t="s">
-        <v>40</v>
+      <c r="B376" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>37</v>
@@ -10061,8 +10064,8 @@
       <c r="A527" s="5">
         <v>526</v>
       </c>
-      <c r="B527" s="6" t="s">
-        <v>54</v>
+      <c r="B527" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C527" s="5" t="s">
         <v>52</v>
@@ -10079,8 +10082,8 @@
       <c r="A528" s="2">
         <v>527</v>
       </c>
-      <c r="B528" s="3" t="s">
-        <v>54</v>
+      <c r="B528" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>52</v>
@@ -10097,8 +10100,8 @@
       <c r="A529" s="5">
         <v>528</v>
       </c>
-      <c r="B529" s="6" t="s">
-        <v>54</v>
+      <c r="B529" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C529" s="5" t="s">
         <v>52</v>
@@ -10115,8 +10118,8 @@
       <c r="A530" s="2">
         <v>529</v>
       </c>
-      <c r="B530" s="3" t="s">
-        <v>54</v>
+      <c r="B530" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>52</v>
@@ -10133,8 +10136,8 @@
       <c r="A531" s="5">
         <v>530</v>
       </c>
-      <c r="B531" s="6" t="s">
-        <v>54</v>
+      <c r="B531" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C531" s="5" t="s">
         <v>52</v>
@@ -10151,8 +10154,8 @@
       <c r="A532" s="2">
         <v>531</v>
       </c>
-      <c r="B532" s="3" t="s">
-        <v>54</v>
+      <c r="B532" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>52</v>
@@ -10169,8 +10172,8 @@
       <c r="A533" s="5">
         <v>532</v>
       </c>
-      <c r="B533" s="6" t="s">
-        <v>54</v>
+      <c r="B533" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C533" s="5" t="s">
         <v>52</v>
@@ -10187,8 +10190,8 @@
       <c r="A534" s="2">
         <v>533</v>
       </c>
-      <c r="B534" s="3" t="s">
-        <v>54</v>
+      <c r="B534" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>52</v>
@@ -10205,8 +10208,8 @@
       <c r="A535" s="5">
         <v>534</v>
       </c>
-      <c r="B535" s="6" t="s">
-        <v>54</v>
+      <c r="B535" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C535" s="5" t="s">
         <v>52</v>
@@ -10223,8 +10226,8 @@
       <c r="A536" s="2">
         <v>535</v>
       </c>
-      <c r="B536" s="3" t="s">
-        <v>54</v>
+      <c r="B536" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>52</v>
@@ -10241,8 +10244,8 @@
       <c r="A537" s="5">
         <v>536</v>
       </c>
-      <c r="B537" s="6" t="s">
-        <v>54</v>
+      <c r="B537" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C537" s="5" t="s">
         <v>52</v>
@@ -10259,8 +10262,8 @@
       <c r="A538" s="2">
         <v>537</v>
       </c>
-      <c r="B538" s="3" t="s">
-        <v>54</v>
+      <c r="B538" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>52</v>
@@ -10277,8 +10280,8 @@
       <c r="A539" s="5">
         <v>538</v>
       </c>
-      <c r="B539" s="6" t="s">
-        <v>54</v>
+      <c r="B539" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C539" s="5" t="s">
         <v>52</v>
@@ -10295,8 +10298,8 @@
       <c r="A540" s="2">
         <v>539</v>
       </c>
-      <c r="B540" s="3" t="s">
-        <v>54</v>
+      <c r="B540" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>52</v>
@@ -10313,8 +10316,8 @@
       <c r="A541" s="5">
         <v>540</v>
       </c>
-      <c r="B541" s="6" t="s">
-        <v>54</v>
+      <c r="B541" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C541" s="5" t="s">
         <v>52</v>
@@ -10331,8 +10334,8 @@
       <c r="A542" s="2">
         <v>541</v>
       </c>
-      <c r="B542" s="3" t="s">
-        <v>55</v>
+      <c r="B542" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>52</v>
@@ -10349,8 +10352,8 @@
       <c r="A543" s="5">
         <v>542</v>
       </c>
-      <c r="B543" s="6" t="s">
-        <v>55</v>
+      <c r="B543" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C543" s="5" t="s">
         <v>52</v>
@@ -10367,8 +10370,8 @@
       <c r="A544" s="2">
         <v>543</v>
       </c>
-      <c r="B544" s="3" t="s">
-        <v>55</v>
+      <c r="B544" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>52</v>
@@ -10385,8 +10388,8 @@
       <c r="A545" s="5">
         <v>544</v>
       </c>
-      <c r="B545" s="6" t="s">
-        <v>55</v>
+      <c r="B545" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C545" s="5" t="s">
         <v>52</v>
@@ -10403,8 +10406,8 @@
       <c r="A546" s="2">
         <v>545</v>
       </c>
-      <c r="B546" s="3" t="s">
-        <v>55</v>
+      <c r="B546" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>52</v>
@@ -10421,8 +10424,8 @@
       <c r="A547" s="5">
         <v>546</v>
       </c>
-      <c r="B547" s="6" t="s">
-        <v>55</v>
+      <c r="B547" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C547" s="5" t="s">
         <v>52</v>
@@ -10439,8 +10442,8 @@
       <c r="A548" s="2">
         <v>547</v>
       </c>
-      <c r="B548" s="3" t="s">
-        <v>55</v>
+      <c r="B548" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>52</v>
@@ -10457,8 +10460,8 @@
       <c r="A549" s="5">
         <v>548</v>
       </c>
-      <c r="B549" s="6" t="s">
-        <v>55</v>
+      <c r="B549" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C549" s="5" t="s">
         <v>52</v>
@@ -10475,8 +10478,8 @@
       <c r="A550" s="2">
         <v>549</v>
       </c>
-      <c r="B550" s="3" t="s">
-        <v>55</v>
+      <c r="B550" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>52</v>
@@ -10493,8 +10496,8 @@
       <c r="A551" s="5">
         <v>550</v>
       </c>
-      <c r="B551" s="6" t="s">
-        <v>55</v>
+      <c r="B551" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C551" s="5" t="s">
         <v>52</v>
@@ -10511,8 +10514,8 @@
       <c r="A552" s="2">
         <v>551</v>
       </c>
-      <c r="B552" s="3" t="s">
-        <v>55</v>
+      <c r="B552" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>52</v>
@@ -10529,8 +10532,8 @@
       <c r="A553" s="5">
         <v>552</v>
       </c>
-      <c r="B553" s="6" t="s">
-        <v>55</v>
+      <c r="B553" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C553" s="5" t="s">
         <v>52</v>
@@ -10547,8 +10550,8 @@
       <c r="A554" s="2">
         <v>553</v>
       </c>
-      <c r="B554" s="3" t="s">
-        <v>55</v>
+      <c r="B554" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>52</v>
@@ -10565,8 +10568,8 @@
       <c r="A555" s="5">
         <v>554</v>
       </c>
-      <c r="B555" s="6" t="s">
-        <v>55</v>
+      <c r="B555" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C555" s="5" t="s">
         <v>52</v>
@@ -10583,8 +10586,8 @@
       <c r="A556" s="2">
         <v>555</v>
       </c>
-      <c r="B556" s="3" t="s">
-        <v>55</v>
+      <c r="B556" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>52</v>
@@ -11951,8 +11954,8 @@
       <c r="A632" s="2">
         <v>631</v>
       </c>
-      <c r="B632" s="3" t="s">
-        <v>63</v>
+      <c r="B632" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>62</v>
@@ -11969,8 +11972,8 @@
       <c r="A633" s="5">
         <v>632</v>
       </c>
-      <c r="B633" s="6" t="s">
-        <v>63</v>
+      <c r="B633" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C633" s="5" t="s">
         <v>62</v>
@@ -11987,8 +11990,8 @@
       <c r="A634" s="2">
         <v>633</v>
       </c>
-      <c r="B634" s="3" t="s">
-        <v>63</v>
+      <c r="B634" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>62</v>
@@ -12006,7 +12009,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C635" s="5" t="s">
         <v>62</v>
@@ -12024,7 +12027,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>62</v>
@@ -12042,7 +12045,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C637" s="5" t="s">
         <v>62</v>
@@ -12059,8 +12062,8 @@
       <c r="A638" s="2">
         <v>637</v>
       </c>
-      <c r="B638" s="3" t="s">
-        <v>63</v>
+      <c r="B638" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>62</v>
@@ -12077,8 +12080,8 @@
       <c r="A639" s="5">
         <v>638</v>
       </c>
-      <c r="B639" s="6" t="s">
-        <v>63</v>
+      <c r="B639" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C639" s="5" t="s">
         <v>62</v>
@@ -12095,8 +12098,8 @@
       <c r="A640" s="2">
         <v>639</v>
       </c>
-      <c r="B640" s="3" t="s">
-        <v>63</v>
+      <c r="B640" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>62</v>
@@ -12114,7 +12117,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C641" s="5" t="s">
         <v>62</v>
@@ -12132,7 +12135,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>62</v>
@@ -12150,7 +12153,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C643" s="5" t="s">
         <v>62</v>
@@ -12167,8 +12170,8 @@
       <c r="A644" s="2">
         <v>643</v>
       </c>
-      <c r="B644" s="3" t="s">
-        <v>63</v>
+      <c r="B644" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>62</v>
@@ -12185,8 +12188,8 @@
       <c r="A645" s="5">
         <v>644</v>
       </c>
-      <c r="B645" s="6" t="s">
-        <v>63</v>
+      <c r="B645" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C645" s="5" t="s">
         <v>62</v>
@@ -12203,8 +12206,8 @@
       <c r="A646" s="2">
         <v>645</v>
       </c>
-      <c r="B646" s="3" t="s">
-        <v>63</v>
+      <c r="B646" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>62</v>
@@ -12491,8 +12494,8 @@
       <c r="A662" s="5">
         <v>661</v>
       </c>
-      <c r="B662" s="6" t="s">
-        <v>65</v>
+      <c r="B662" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C662" s="5" t="s">
         <v>62</v>
@@ -12509,8 +12512,8 @@
       <c r="A663" s="2">
         <v>662</v>
       </c>
-      <c r="B663" s="3" t="s">
-        <v>65</v>
+      <c r="B663" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>62</v>
@@ -12527,8 +12530,8 @@
       <c r="A664" s="5">
         <v>663</v>
       </c>
-      <c r="B664" s="6" t="s">
-        <v>65</v>
+      <c r="B664" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C664" s="5" t="s">
         <v>62</v>
@@ -12546,7 +12549,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C665" s="5" t="s">
         <v>62</v>
@@ -12564,7 +12567,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>62</v>
@@ -12582,7 +12585,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C667" s="5" t="s">
         <v>62</v>
@@ -12599,8 +12602,8 @@
       <c r="A668" s="5">
         <v>667</v>
       </c>
-      <c r="B668" s="6" t="s">
-        <v>65</v>
+      <c r="B668" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C668" s="5" t="s">
         <v>62</v>
@@ -12617,8 +12620,8 @@
       <c r="A669" s="2">
         <v>668</v>
       </c>
-      <c r="B669" s="3" t="s">
-        <v>65</v>
+      <c r="B669" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>62</v>
@@ -12635,8 +12638,8 @@
       <c r="A670" s="5">
         <v>669</v>
       </c>
-      <c r="B670" s="6" t="s">
-        <v>65</v>
+      <c r="B670" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C670" s="5" t="s">
         <v>62</v>
@@ -12654,7 +12657,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C671" s="5" t="s">
         <v>62</v>
@@ -12672,7 +12675,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>62</v>
@@ -12690,7 +12693,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C673" s="5" t="s">
         <v>62</v>
@@ -12707,8 +12710,8 @@
       <c r="A674" s="5">
         <v>673</v>
       </c>
-      <c r="B674" s="6" t="s">
-        <v>65</v>
+      <c r="B674" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C674" s="5" t="s">
         <v>62</v>
@@ -12725,8 +12728,8 @@
       <c r="A675" s="2">
         <v>674</v>
       </c>
-      <c r="B675" s="3" t="s">
-        <v>65</v>
+      <c r="B675" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>62</v>
@@ -12743,8 +12746,8 @@
       <c r="A676" s="5">
         <v>675</v>
       </c>
-      <c r="B676" s="6" t="s">
-        <v>65</v>
+      <c r="B676" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C676" s="5" t="s">
         <v>62</v>
@@ -13311,7 +13314,7 @@
         <v>8</v>
       </c>
       <c r="E707" s="4">
-        <f t="shared" ref="E707:E736" si="31">E706+1</f>
+        <f t="shared" ref="E707" si="31">E706+1</f>
         <v>48</v>
       </c>
     </row>
